--- a/SuppXLS/Trades/ScenTrade__Trade_Links.xlsx
+++ b/SuppXLS/Trades/ScenTrade__Trade_Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SuppXLS\Trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8959AEB8-2D1A-4792-B9AB-8644B7CDF079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D9A59A-A8C0-4DC3-9E31-2D8C2516812B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>~Tradelinks</t>
   </si>
   <si>
-    <t>GBL</t>
-  </si>
-  <si>
     <t>Region</t>
   </si>
   <si>
@@ -171,6 +168,9 @@
   </si>
   <si>
     <t>Ukraine</t>
+  </si>
+  <si>
+    <t>\I:Africa_North</t>
   </si>
 </sst>
 </file>
@@ -532,7 +532,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1">
         <v>1</v>
@@ -567,7 +567,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.45">
@@ -575,7 +575,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
         <v>0</v>
@@ -604,56 +604,56 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="str">
         <f>VLOOKUP(D1,$A$1:$B$27,2,FALSE)</f>
         <v>m_lithium</v>
       </c>
-      <c r="E4" t="s">
-        <v>1</v>
+      <c r="E4" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="G4" t="str">
         <f>VLOOKUP(G1,$A$1:$B$27,2,FALSE)</f>
         <v>m_nickel</v>
       </c>
-      <c r="H4" t="s">
-        <v>1</v>
+      <c r="H4" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="J4" t="str">
         <f>VLOOKUP(J1,$A$1:$B$27,2,FALSE)</f>
         <v>m_cobalt</v>
       </c>
-      <c r="K4" t="s">
-        <v>1</v>
+      <c r="K4" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="M4" t="str">
         <f>VLOOKUP(M1,$A$1:$B$27,2,FALSE)</f>
         <v>m_manganese</v>
       </c>
-      <c r="N4" t="s">
-        <v>1</v>
+      <c r="N4" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="P4" t="str">
         <f>VLOOKUP(P1,$A$1:$B$27,2,FALSE)</f>
         <v>m_aluminum</v>
       </c>
-      <c r="Q4" t="s">
-        <v>1</v>
+      <c r="Q4" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="S4" t="str">
         <f>VLOOKUP(S1,$A$1:$B$27,2,FALSE)</f>
         <v>m_copper</v>
       </c>
-      <c r="T4" t="s">
-        <v>1</v>
+      <c r="T4" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="V4" t="str">
         <f>VLOOKUP(V1,$A$1:$B$27,2,FALSE)</f>
         <v>m_graphite</v>
       </c>
-      <c r="W4" t="s">
-        <v>1</v>
+      <c r="W4" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
@@ -661,11 +661,11 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="str">
         <f>IF(A37="","\I:",A37)</f>
-        <v>Africa_North</v>
+        <v>\I:Africa_North</v>
       </c>
       <c r="E5" t="str">
         <f>"GlbMarket_"&amp;VLOOKUP(D1,$A$1:$B$29,2,FALSE)</f>
@@ -673,7 +673,7 @@
       </c>
       <c r="G5" t="str">
         <f>IF($D5="","\I:",$D5)</f>
-        <v>Africa_North</v>
+        <v>\I:Africa_North</v>
       </c>
       <c r="H5" t="str">
         <f>"GlbMarket_"&amp;VLOOKUP(G1,$A$1:$B$29,2,FALSE)</f>
@@ -681,7 +681,7 @@
       </c>
       <c r="J5" t="str">
         <f>$D5</f>
-        <v>Africa_North</v>
+        <v>\I:Africa_North</v>
       </c>
       <c r="K5" t="str">
         <f>"GlbMarket_"&amp;VLOOKUP(J1,$A$1:$B$29,2,FALSE)</f>
@@ -689,7 +689,7 @@
       </c>
       <c r="M5" t="str">
         <f>$D5</f>
-        <v>Africa_North</v>
+        <v>\I:Africa_North</v>
       </c>
       <c r="N5" t="str">
         <f>"GlbMarket_"&amp;VLOOKUP(M1,$A$1:$B$29,2,FALSE)</f>
@@ -697,7 +697,7 @@
       </c>
       <c r="P5" t="str">
         <f>$D5</f>
-        <v>Africa_North</v>
+        <v>\I:Africa_North</v>
       </c>
       <c r="Q5" t="str">
         <f>"GlbMarket_"&amp;VLOOKUP(P1,$A$1:$B$29,2,FALSE)</f>
@@ -705,7 +705,7 @@
       </c>
       <c r="S5" t="str">
         <f>$D5</f>
-        <v>Africa_North</v>
+        <v>\I:Africa_North</v>
       </c>
       <c r="T5" t="str">
         <f>"GlbMarket_"&amp;VLOOKUP(S1,$A$1:$B$29,2,FALSE)</f>
@@ -713,7 +713,7 @@
       </c>
       <c r="V5" t="str">
         <f>$D5</f>
-        <v>Africa_North</v>
+        <v>\I:Africa_North</v>
       </c>
       <c r="W5" t="str">
         <f>"GlbMarket_"&amp;VLOOKUP(V1,$A$1:$B$29,2,FALSE)</f>
@@ -725,7 +725,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="str">
         <f t="shared" ref="D6:D34" si="0">IF(A38="","\I:",A38)</f>
@@ -789,7 +789,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2482,182 +2482,182 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Trades/ScenTrade__Trade_Links.xlsx
+++ b/SuppXLS/Trades/ScenTrade__Trade_Links.xlsx
@@ -1,14 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SuppXLS\Trades\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D105A8D-18C7-4741-889A-55CEFDB11A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bi - markets" sheetId="5" r:id="rId1"/>
     <sheet name="Bi - markets_RecyMat_XiaoAdd" sheetId="6" r:id="rId2"/>
+    <sheet name="ELC_Trades" sheetId="7" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="TradeLinks">#REF!</definedName>
@@ -31,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="198">
   <si>
     <t>m_lithium</t>
   </si>
@@ -187,24 +194,463 @@
   </si>
   <si>
     <t>m_fromrecy_graphite</t>
+  </si>
+  <si>
+    <t>Reg1</t>
+  </si>
+  <si>
+    <t>Reg2</t>
+  </si>
+  <si>
+    <t>Comm</t>
+  </si>
+  <si>
+    <t>Comm1</t>
+  </si>
+  <si>
+    <t>Comm2</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>TradeLink</t>
+  </si>
+  <si>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_North-Africa_Other</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_North-GreeceCyp</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_North-ItalyMal</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_North-MidEast</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_North-SaudiArabia</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_North-SpainPor</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_Other-Africa_North</t>
+  </si>
+  <si>
+    <t>TU_ELC_Africa_Other-SouthAfrica</t>
+  </si>
+  <si>
+    <t>TU_ELC_Austria-CroSloven</t>
+  </si>
+  <si>
+    <t>TU_ELC_Austria-CzechSlovak</t>
+  </si>
+  <si>
+    <t>TU_ELC_Austria-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_Austria-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_Austria-ItalyMal</t>
+  </si>
+  <si>
+    <t>TU_ELC_Austria-Switzerland</t>
+  </si>
+  <si>
+    <t>TU_ELC_Baltics-Poland</t>
+  </si>
+  <si>
+    <t>TU_ELC_Baltics-Russia</t>
+  </si>
+  <si>
+    <t>TU_ELC_Baltics-SweFinDen</t>
+  </si>
+  <si>
+    <t>TU_ELC_BeNeLux-France</t>
+  </si>
+  <si>
+    <t>TU_ELC_BeNeLux-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_BeNeLux-Norway</t>
+  </si>
+  <si>
+    <t>TU_ELC_BeNeLux-SweFinDen</t>
+  </si>
+  <si>
+    <t>TU_ELC_BeNeLux-UK</t>
+  </si>
+  <si>
+    <t>TU_ELC_Brazil-LatAm</t>
+  </si>
+  <si>
+    <t>TU_ELC_China-ROW</t>
+  </si>
+  <si>
+    <t>TU_ELC_China-Russia</t>
+  </si>
+  <si>
+    <t>TU_ELC_CroSloven-Austria</t>
+  </si>
+  <si>
+    <t>TU_ELC_CroSloven-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_CroSloven-ItalyMal</t>
+  </si>
+  <si>
+    <t>TU_ELC_CroSloven-WestBalkans</t>
+  </si>
+  <si>
+    <t>TU_ELC_CzechSlovak-Austria</t>
+  </si>
+  <si>
+    <t>TU_ELC_CzechSlovak-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_CzechSlovak-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_CzechSlovak-Poland</t>
+  </si>
+  <si>
+    <t>TU_ELC_CzechSlovak-Ukraine</t>
+  </si>
+  <si>
+    <t>TU_ELC_France-BeNeLux</t>
+  </si>
+  <si>
+    <t>TU_ELC_France-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_France-Ireland</t>
+  </si>
+  <si>
+    <t>TU_ELC_France-ItalyMal</t>
+  </si>
+  <si>
+    <t>TU_ELC_France-SpainPor</t>
+  </si>
+  <si>
+    <t>TU_ELC_France-Switzerland</t>
+  </si>
+  <si>
+    <t>TU_ELC_France-UK</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-Austria</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-BeNeLux</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-CzechSlovak</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-France</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-Norway</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-Poland</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-SweFinDen</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-Switzerland</t>
+  </si>
+  <si>
+    <t>TU_ELC_Germany-UK</t>
+  </si>
+  <si>
+    <t>TU_ELC_GreeceCyp-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_GreeceCyp-Africa_North</t>
+  </si>
+  <si>
+    <t>TU_ELC_GreeceCyp-ItalyMal</t>
+  </si>
+  <si>
+    <t>TU_ELC_GreeceCyp-Turkey</t>
+  </si>
+  <si>
+    <t>TU_ELC_GreeceCyp-WestBalkans</t>
+  </si>
+  <si>
+    <t>TU_ELC_GreeceCyp-MidEast</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-Austria</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-CroSloven</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-CzechSlovak</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-GreeceCyp</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-ROW</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-Turkey</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-Ukraine</t>
+  </si>
+  <si>
+    <t>TU_ELC_HunRomBul-WestBalkans</t>
+  </si>
+  <si>
+    <t>TU_ELC_Iceland-UK</t>
+  </si>
+  <si>
+    <t>TU_ELC_India-ROW</t>
+  </si>
+  <si>
+    <t>TU_ELC_Ireland-France</t>
+  </si>
+  <si>
+    <t>TU_ELC_Ireland-UK</t>
+  </si>
+  <si>
+    <t>TU_ELC_ItalyMal-Africa_North</t>
+  </si>
+  <si>
+    <t>TU_ELC_ItalyMal-Austria</t>
+  </si>
+  <si>
+    <t>TU_ELC_ItalyMal-CroSloven</t>
+  </si>
+  <si>
+    <t>TU_ELC_ItalyMal-France</t>
+  </si>
+  <si>
+    <t>TU_ELC_ItalyMal-GreeceCyp</t>
+  </si>
+  <si>
+    <t>TU_ELC_ItalyMal-Switzerland</t>
+  </si>
+  <si>
+    <t>TU_ELC_ItalyMal-WestBalkans</t>
+  </si>
+  <si>
+    <t>TU_ELC_LatAm-Brazil</t>
+  </si>
+  <si>
+    <t>TU_ELC_LatAm-NorthAm</t>
+  </si>
+  <si>
+    <t>TU_ELC_MidEast-Africa_North</t>
+  </si>
+  <si>
+    <t>TU_ELC_MidEast-ROW</t>
+  </si>
+  <si>
+    <t>TU_ELC_MidEast-SaudiArabia</t>
+  </si>
+  <si>
+    <t>TU_ELC_MidEast-Turkey</t>
+  </si>
+  <si>
+    <t>TU_ELC_MidEast-GreeceCyp</t>
+  </si>
+  <si>
+    <t>TU_ELC_NorthAm-LatAm</t>
+  </si>
+  <si>
+    <t>TU_ELC_Norway-BeNeLux</t>
+  </si>
+  <si>
+    <t>TU_ELC_Norway-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_Norway-SweFinDen</t>
+  </si>
+  <si>
+    <t>TU_ELC_Norway-UK</t>
+  </si>
+  <si>
+    <t>TU_ELC_Poland-Baltics</t>
+  </si>
+  <si>
+    <t>TU_ELC_Poland-CzechSlovak</t>
+  </si>
+  <si>
+    <t>TU_ELC_Poland-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_Poland-SweFinDen</t>
+  </si>
+  <si>
+    <t>TU_ELC_Poland-Ukraine</t>
+  </si>
+  <si>
+    <t>TU_ELC_ROW-China</t>
+  </si>
+  <si>
+    <t>TU_ELC_ROW-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_ROW-India</t>
+  </si>
+  <si>
+    <t>TU_ELC_ROW-MidEast</t>
+  </si>
+  <si>
+    <t>TU_ELC_ROW-Russia</t>
+  </si>
+  <si>
+    <t>TU_ELC_ROW-Turkey</t>
+  </si>
+  <si>
+    <t>TU_ELC_ROW-Ukraine</t>
+  </si>
+  <si>
+    <t>TU_ELC_Russia-Baltics</t>
+  </si>
+  <si>
+    <t>TU_ELC_Russia-China</t>
+  </si>
+  <si>
+    <t>TU_ELC_Russia-ROW</t>
+  </si>
+  <si>
+    <t>TU_ELC_SaudiArabia-Africa_North</t>
+  </si>
+  <si>
+    <t>TU_ELC_SaudiArabia-MidEast</t>
+  </si>
+  <si>
+    <t>TU_ELC_SouthAfrica-Africa_Other</t>
+  </si>
+  <si>
+    <t>TU_ELC_SpainPor-Africa_North</t>
+  </si>
+  <si>
+    <t>TU_ELC_SpainPor-France</t>
+  </si>
+  <si>
+    <t>TU_ELC_SweFinDen-Baltics</t>
+  </si>
+  <si>
+    <t>TU_ELC_SweFinDen-BeNeLux</t>
+  </si>
+  <si>
+    <t>TU_ELC_SweFinDen-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_SweFinDen-Norway</t>
+  </si>
+  <si>
+    <t>TU_ELC_SweFinDen-Poland</t>
+  </si>
+  <si>
+    <t>TU_ELC_SweFinDen-UK</t>
+  </si>
+  <si>
+    <t>TU_ELC_Switzerland-Austria</t>
+  </si>
+  <si>
+    <t>TU_ELC_Switzerland-France</t>
+  </si>
+  <si>
+    <t>TU_ELC_Switzerland-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_Switzerland-ItalyMal</t>
+  </si>
+  <si>
+    <t>TU_ELC_Turkey-GreeceCyp</t>
+  </si>
+  <si>
+    <t>TU_ELC_Turkey-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_Turkey-MidEast</t>
+  </si>
+  <si>
+    <t>TU_ELC_Turkey-ROW</t>
+  </si>
+  <si>
+    <t>TU_ELC_UK-BeNeLux</t>
+  </si>
+  <si>
+    <t>TU_ELC_UK-France</t>
+  </si>
+  <si>
+    <t>TU_ELC_UK-Germany</t>
+  </si>
+  <si>
+    <t>TU_ELC_UK-Iceland</t>
+  </si>
+  <si>
+    <t>TU_ELC_UK-Ireland</t>
+  </si>
+  <si>
+    <t>TU_ELC_UK-Norway</t>
+  </si>
+  <si>
+    <t>TU_ELC_UK-SweFinDen</t>
+  </si>
+  <si>
+    <t>TU_ELC_Ukraine-CzechSlovak</t>
+  </si>
+  <si>
+    <t>TU_ELC_Ukraine-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_Ukraine-Poland</t>
+  </si>
+  <si>
+    <t>TU_ELC_Ukraine-ROW</t>
+  </si>
+  <si>
+    <t>TU_ELC_WestBalkans-CroSloven</t>
+  </si>
+  <si>
+    <t>TU_ELC_WestBalkans-GreeceCyp</t>
+  </si>
+  <si>
+    <t>TU_ELC_WestBalkans-HunRomBul</t>
+  </si>
+  <si>
+    <t>TU_ELC_WestBalkans-ItalyMal</t>
+  </si>
+  <si>
+    <t>~TradeLinks_DINS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -215,144 +661,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,7 +677,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,182 +687,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -554,308 +696,33 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="35"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="23"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="4">
+    <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{743D950F-DCA2-4CC3-98AB-BCEE9F80E264}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1113,19 +980,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="14.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="17.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="14.6363636363636" customWidth="1"/>
-    <col min="8" max="8" width="17.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" customWidth="1"/>
+    <col min="5" max="5" width="17.73046875" customWidth="1"/>
+    <col min="7" max="7" width="14.59765625" customWidth="1"/>
+    <col min="8" max="8" width="17.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -3083,7 +2950,7 @@
     </row>
     <row r="35" spans="1:23">
       <c r="D35" s="1" t="str">
-        <f t="shared" ref="D35:D40" si="14">IF(A67="","\I:",A67)</f>
+        <f t="shared" ref="D35:D39" si="14">IF(A67="","\I:",A67)</f>
         <v>Switzerland</v>
       </c>
       <c r="E35" t="str">
@@ -3546,22 +3413,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="12.2636363636364" customWidth="1"/>
-    <col min="5" max="5" width="30.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="14.6363636363636" customWidth="1"/>
-    <col min="8" max="8" width="17.7272727272727" customWidth="1"/>
-    <col min="11" max="11" width="29.9090909090909" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="4" max="4" width="12.265625" customWidth="1"/>
+    <col min="5" max="5" width="30.73046875" customWidth="1"/>
+    <col min="7" max="7" width="14.59765625" customWidth="1"/>
+    <col min="8" max="8" width="17.73046875" customWidth="1"/>
+    <col min="11" max="11" width="29.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -5519,59 +5384,59 @@
     </row>
     <row r="35" spans="1:23">
       <c r="D35" s="1" t="str">
-        <f t="shared" ref="D35:D40" si="14">IF(A67="","\I:",A67)</f>
+        <f t="shared" ref="D35:D39" si="14">IF(A67="","\I:",A67)</f>
         <v>Switzerland</v>
       </c>
       <c r="E35" t="str">
-        <f t="shared" ref="E35:E40" si="15">E34</f>
+        <f t="shared" ref="E35:E39" si="15">E34</f>
         <v>GlbMarket_m_fromrecy_lithium</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" ref="G35:G40" si="16">$D35</f>
+        <f t="shared" ref="G35:G39" si="16">$D35</f>
         <v>Switzerland</v>
       </c>
       <c r="H35" t="str">
-        <f t="shared" ref="H35:H40" si="17">H34</f>
+        <f t="shared" ref="H35:H39" si="17">H34</f>
         <v>GlbMarket_m_fromrecy_nickel</v>
       </c>
       <c r="J35" t="str">
-        <f t="shared" ref="J35:J40" si="18">$D35</f>
+        <f t="shared" ref="J35:J39" si="18">$D35</f>
         <v>Switzerland</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" ref="K35:K40" si="19">K34</f>
+        <f t="shared" ref="K35:K39" si="19">K34</f>
         <v>GlbMarket_m_fromrecy_cobalt</v>
       </c>
       <c r="M35" t="str">
-        <f t="shared" ref="M35:M40" si="20">$D35</f>
+        <f t="shared" ref="M35:M39" si="20">$D35</f>
         <v>Switzerland</v>
       </c>
       <c r="N35" t="str">
-        <f t="shared" ref="N35:N40" si="21">N34</f>
+        <f t="shared" ref="N35:N39" si="21">N34</f>
         <v>GlbMarket_m_fromrecy_manganese</v>
       </c>
       <c r="P35" t="str">
-        <f t="shared" ref="P35:P40" si="22">$D35</f>
+        <f t="shared" ref="P35:P39" si="22">$D35</f>
         <v>Switzerland</v>
       </c>
       <c r="Q35" t="str">
-        <f t="shared" ref="Q35:Q40" si="23">Q34</f>
+        <f t="shared" ref="Q35:Q39" si="23">Q34</f>
         <v>GlbMarket_m_fromrecy_aluminum</v>
       </c>
       <c r="S35" t="str">
-        <f t="shared" ref="S35:S40" si="24">$D35</f>
+        <f t="shared" ref="S35:S39" si="24">$D35</f>
         <v>Switzerland</v>
       </c>
       <c r="T35" t="str">
-        <f t="shared" ref="T35:T40" si="25">T34</f>
+        <f t="shared" ref="T35:T39" si="25">T34</f>
         <v>GlbMarket_m_fromrecy_copper</v>
       </c>
       <c r="V35" t="str">
-        <f t="shared" ref="V35:V40" si="26">$D35</f>
+        <f t="shared" ref="V35:V39" si="26">$D35</f>
         <v>Switzerland</v>
       </c>
       <c r="W35" t="str">
-        <f t="shared" ref="W35:W40" si="27">W34</f>
+        <f t="shared" ref="W35:W39" si="27">W34</f>
         <v>GlbMarket_m_fromrecy_graphite</v>
       </c>
     </row>
@@ -5982,6 +5847,3185 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD5BCDA-D168-4CA3-B158-396E4F69B597}">
+  <dimension ref="A1:G138"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="14.53125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.06640625" style="3"/>
+    <col min="9" max="9" width="14.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>